--- a/sequences/learning_blockA_fixed-middle-10_05.xlsx
+++ b/sequences/learning_blockA_fixed-middle-10_05.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
         <v>12</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -668,17 +668,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>12</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -762,44 +762,44 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_17.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_31.jpg</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>right</t>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -830,16 +830,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" t="n">
         <v>4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -861,84 +861,84 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -960,84 +960,84 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1059,52 +1059,52 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/phone/phone_08.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1113,30 +1113,30 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S7" t="n">
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1158,84 +1158,84 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0.1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1257,84 +1257,84 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_17.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>stimuli/fish/fish_07.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_10.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
         <v>6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,49 +1391,49 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P10" t="n">
         <v>0.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S10" t="n">
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
         <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1455,47 +1455,47 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1505,34 +1505,34 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>0.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1554,84 +1554,84 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S12" t="n">
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1703,34 +1703,34 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>15</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1806,14 +1806,14 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>0.1</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1826,10 +1826,10 @@
         <v>17</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,22 +1881,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1905,14 +1905,14 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1925,10 +1925,10 @@
         <v>12</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1975,43 +1975,43 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2021,13 +2021,13 @@
         <v>12</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2049,47 +2049,47 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/phone/phone_08.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2099,34 +2099,34 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/phone/phone_08.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2168,17 +2168,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2188,41 +2188,41 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W18" t="n">
         <v>12</v>
@@ -2247,47 +2247,47 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_31.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>stimuli/pencil/pencil_10.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_10.jpg</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>pencil</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2308,23 +2308,23 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S19" t="n">
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
         <v>16</v>
       </c>
       <c r="W19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2346,84 +2346,84 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>stimuli/house/house_15.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_26.jpg</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S20" t="n">
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" t="n">
         <v>8</v>
       </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
       <c r="W20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2445,42 +2445,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2490,19 +2490,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -2544,84 +2544,84 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2643,84 +2643,84 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_33.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_08.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_11.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_17.jpg</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S23" t="n">
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>17</v>
+      </c>
+      <c r="W23" t="n">
         <v>9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>15</v>
-      </c>
-      <c r="W23" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -2742,44 +2742,44 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_31.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_10.jpg</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>center</t>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2810,16 +2810,16 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
         <v>10</v>
-      </c>
-      <c r="W24" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2841,84 +2841,84 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_26.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_10.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_11.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_08.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>0.4</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S25" t="n">
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" t="n">
         <v>5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>10</v>
-      </c>
-      <c r="V25" t="n">
-        <v>17</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2985,19 +2985,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3069,38 +3069,38 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,10 +3113,10 @@
         <v>17</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -3242,17 +3242,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3262,22 +3262,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3287,18 +3287,18 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -3308,13 +3308,13 @@
         <v>12</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3376,17 +3376,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -3397,20 +3397,20 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
         <v>15</v>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3496,20 +3496,20 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S31" t="n">
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
         <v>17</v>
@@ -3534,52 +3534,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3588,30 +3588,30 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S32" t="n">
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3694,23 +3694,23 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V33" t="n">
         <v>12</v>
       </c>
       <c r="W33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3732,52 +3732,52 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_10.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_10.jpg</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>pencil</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3786,30 +3786,30 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S34" t="n">
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W34" t="n">
         <v>16</v>
-      </c>
-      <c r="W34" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -3831,44 +3831,44 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_17.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_15.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>right</t>
@@ -3876,19 +3876,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U35" t="n">
+        <v>8</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" t="n">
         <v>6</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9</v>
-      </c>
-      <c r="W35" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3965,49 +3965,49 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P36" t="n">
         <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S36" t="n">
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V36" t="n">
         <v>12</v>
       </c>
       <c r="W36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -4029,52 +4029,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4083,30 +4083,30 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -4128,42 +4128,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4173,19 +4173,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4237,17 +4237,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,54 +4257,54 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S39" t="n">
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
       </c>
       <c r="V39" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4356,38 +4356,38 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4400,10 +4400,10 @@
         <v>17</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,38 +4455,38 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="Q41" t="n">
         <v>0.2</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>12</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4564,28 +4564,28 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q42" t="n">
         <v>0.2</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -4595,10 +4595,10 @@
         <v>12</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
         <v>15</v>
@@ -4623,47 +4623,47 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_31.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_17.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_15.jpg</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4673,34 +4673,34 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q43" t="n">
         <v>0.5</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
+        <v>3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>6</v>
+      </c>
+      <c r="W43" t="n">
         <v>7</v>
-      </c>
-      <c r="V43" t="n">
-        <v>8</v>
-      </c>
-      <c r="W43" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="44">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4776,27 +4776,27 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q44" t="n">
         <v>0.3</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S44" t="n">
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W44" t="n">
         <v>17</v>
@@ -4821,52 +4821,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4875,30 +4875,30 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S45" t="n">
         <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -4920,47 +4920,47 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>stimuli/house/house_15.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_27.jpg</t>
-        </is>
-      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4970,34 +4970,34 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q46" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S46" t="n">
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U46" t="n">
+        <v>9</v>
+      </c>
+      <c r="V46" t="n">
         <v>8</v>
       </c>
-      <c r="V46" t="n">
-        <v>5</v>
-      </c>
       <c r="W46" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -5019,52 +5019,52 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5073,30 +5073,30 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S47" t="n">
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="W47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -5118,84 +5118,84 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S48" t="n">
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V48" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -5217,84 +5217,84 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S49" t="n">
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W49" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
@@ -5316,44 +5316,44 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_33.jpg</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_26.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_27.jpg</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_10.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>right</t>
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
+        <v>7</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>3</v>
+      </c>
+      <c r="W50" t="n">
         <v>9</v>
-      </c>
-      <c r="U50" t="n">
-        <v>5</v>
-      </c>
-      <c r="V50" t="n">
-        <v>4</v>
-      </c>
-      <c r="W50" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5430,17 +5430,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5472,27 +5472,27 @@
         <v>0.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S51" t="n">
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
         <v>12</v>
       </c>
       <c r="W51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5524,17 +5524,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5564,34 +5564,34 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S52" t="n">
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U52" t="n">
         <v>15</v>
       </c>
       <c r="V52" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="W52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5648,22 +5648,22 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S53" t="n">
@@ -5690,7 +5690,7 @@
         <v>12</v>
       </c>
       <c r="W53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5742,38 +5742,38 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,10 +5786,10 @@
         <v>12</v>
       </c>
       <c r="V54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W54" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/phone/phone_08.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5836,17 +5836,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5882,13 +5882,13 @@
         <v>12</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W55" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -5910,17 +5910,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5930,17 +5930,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5950,41 +5950,41 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q56" t="n">
         <v>0.3</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S56" t="n">
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W56" t="n">
         <v>15</v>
@@ -6009,44 +6009,44 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_27.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_15.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_26.jpg</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>left</t>
@@ -6054,19 +6054,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -6077,16 +6077,16 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
+      </c>
+      <c r="V57" t="n">
+        <v>9</v>
+      </c>
+      <c r="W57" t="n">
         <v>7</v>
-      </c>
-      <c r="U57" t="n">
-        <v>3</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -6108,17 +6108,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6128,17 +6128,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q58" t="n">
         <v>0.2</v>
@@ -6176,13 +6176,13 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W58" t="n">
         <v>16</v>
@@ -6207,47 +6207,47 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>stimuli/house/house_15.jpg</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_31.jpg</t>
-        </is>
-      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/phone/phone_08.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6257,34 +6257,34 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P59" t="n">
         <v>0.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S59" t="n">
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
+        <v>9</v>
+      </c>
+      <c r="V59" t="n">
         <v>8</v>
       </c>
-      <c r="V59" t="n">
-        <v>6</v>
-      </c>
       <c r="W59" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -6306,42 +6306,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -6374,16 +6374,16 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W60" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -6405,47 +6405,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6455,34 +6455,34 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S61" t="n">
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V61" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -6504,47 +6504,47 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6554,34 +6554,34 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S62" t="n">
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V62" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="W62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -6603,42 +6603,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_26.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>dog</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6657,10 +6657,10 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
         <v>5</v>
       </c>
-      <c r="V63" t="n">
-        <v>7</v>
-      </c>
       <c r="W63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -6702,84 +6702,84 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S64" t="n">
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V64" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,54 +6831,54 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S65" t="n">
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U65" t="n">
         <v>15</v>
       </c>
       <c r="V65" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="W65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,17 +6930,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6950,18 +6950,18 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6974,10 +6974,10 @@
         <v>17</v>
       </c>
       <c r="V66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -7009,14 +7009,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_27.jpg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_15.jpg</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>pencil</t>
@@ -7029,22 +7029,22 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7053,14 +7053,14 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,10 +7073,10 @@
         <v>12</v>
       </c>
       <c r="V67" t="n">
+        <v>5</v>
+      </c>
+      <c r="W67" t="n">
         <v>4</v>
-      </c>
-      <c r="W67" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7123,22 +7123,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7148,18 +7148,18 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -7169,13 +7169,13 @@
         <v>12</v>
       </c>
       <c r="U68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W68" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -7197,52 +7197,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>key</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7251,30 +7251,30 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S69" t="n">
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -7296,52 +7296,52 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_27.jpg</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_37.jpg</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_26.jpg</t>
-        </is>
-      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>stimuli/key/key_11.jpg</t>
+          <t>stimuli/phone/phone_08.jpg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7350,30 +7350,30 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S70" t="n">
         <v>5</v>
       </c>
       <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>5</v>
+      </c>
+      <c r="V70" t="n">
         <v>7</v>
       </c>
-      <c r="U70" t="n">
-        <v>3</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
       <c r="W70" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
@@ -7395,52 +7395,52 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_27.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7452,27 +7452,27 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S71" t="n">
         <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -7494,52 +7494,52 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_14.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_10.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7548,30 +7548,30 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S72" t="n">
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V72" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W72" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -7593,84 +7593,84 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_11.jpg</t>
-        </is>
-      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S73" t="n">
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U73" t="n">
+        <v>10</v>
+      </c>
+      <c r="V73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
-        <v>15</v>
-      </c>
       <c r="W73" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -7692,52 +7692,52 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_07.jpg</t>
+          <t>stimuli/key/key_11.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_14.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>key</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7746,30 +7746,30 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S74" t="n">
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V74" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -7791,52 +7791,52 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_17.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_33.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>stimuli/fish/fish_07.jpg</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_15.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_08.jpg</t>
-        </is>
-      </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7845,30 +7845,30 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S75" t="n">
         <v>10</v>
       </c>
       <c r="T75" t="n">
+        <v>8</v>
+      </c>
+      <c r="U75" t="n">
+        <v>7</v>
+      </c>
+      <c r="V75" t="n">
+        <v>12</v>
+      </c>
+      <c r="W75" t="n">
         <v>6</v>
-      </c>
-      <c r="U75" t="n">
-        <v>9</v>
-      </c>
-      <c r="V75" t="n">
-        <v>10</v>
-      </c>
-      <c r="W75" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -7890,42 +7890,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/house/house_15.jpg</t>
+          <t>stimuli/hammer/hammer_33.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_08.jpg</t>
+          <t>stimuli/flower/flower_31.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_17.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V76" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="W76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -7989,84 +7989,84 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_27.jpg</t>
+          <t>stimuli/ball/ball_26.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S77" t="n">
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/chair/chair_10.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8098,17 +8098,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_33.jpg</t>
+          <t>stimuli/pencil/pencil_10.jpg</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_26.jpg</t>
+          <t>stimuli/hand/hand_17.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8118,54 +8118,54 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S78" t="n">
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U78" t="n">
         <v>15</v>
       </c>
       <c r="V78" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W78" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_10.jpg</t>
+          <t>stimuli/fish/fish_07.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_31.jpg</t>
+          <t>stimuli/house/house_15.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -8261,10 +8261,10 @@
         <v>17</v>
       </c>
       <c r="V79" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W79" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
